--- a/data/信用债发行汇总_2026-08-26.xlsx
+++ b/data/信用债发行汇总_2026-08-26.xlsx
@@ -1170,7 +1170,9 @@
           <t>2.15 ~ 2.30</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="n">
+        <v>2.3</v>
+      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>珠海华发集团有限公司</t>

--- a/data/信用债发行汇总_2026-08-26.xlsx
+++ b/data/信用债发行汇总_2026-08-26.xlsx
@@ -8495,7 +8495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AN31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8742,6 +8742,5332 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>26保利久联CP003</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>042680298.IB</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>0.49Y</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2.64 ~ 3.64</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>保利久联控股集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>贵州省-贵阳市</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>25保利久联MTN001</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>190D</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>3.6560</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>贵阳银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>短期融资券(CP)</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>国有企业</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>保利久联控股集团有限责任公司2026年度第三期短期融资券</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>2027-02-22</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>化工制造</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>化学制品</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>化学制品</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>化学制品</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>26威高MTN003(科创债)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>102683369.IB</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2.40 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>威高集团有限公司</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>山东省-威海市</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>26威高MTN002(科创债)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>2.66Y</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2.7328</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>招商银行股份有限公司,青岛银行股份有限公司,中信银行股份有限公司,华夏银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>民营企业</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>威高集团有限公司2026年度第三期科技创新债券</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>医药制造</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>医疗器械制造</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>医疗器械制造</t>
+        </is>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>医疗器械</t>
+        </is>
+      </c>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK3" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL3" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>08-25 19:00</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>26西经发</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>245975.SH</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2.30 ~ 3.50</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>西安经发集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>陕西省-西安市</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>26经发F2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4.91Y</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2.8636</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>天风证券股份有限公司,五矿证券有限公司</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>西安经发集团有限责任公司2026年面向专业投资者公开发行公司债券</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL4" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>26长发集团MTN002B</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>102690015.IB</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2.50 ~ 3.50</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>长春市城市发展投资控股(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>吉林省-长春市</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>25长发集团MTN001B</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3.37Y</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2.0592</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>中国银河证券股份有限公司,吉林银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>长春市城市发展投资控股(集团)有限公司2026年度第二期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-26</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK5" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL5" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>26皖投集MTN004</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>102683367.IB</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2.30 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>安徽省投资集团控股有限公司</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>安徽省</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>25皖投集MTN004(科创债)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>19.23Y</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2.3597</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>安徽省投资集团控股有限公司2026年度第四期中期票据</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>2056-08-27</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK6" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL6" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN6" s="2" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>08-25 19:00</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>26大集GT01</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>520434.SZ</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>山东大集控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>山东省-临沂市</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>26大集01</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4.39Y</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2.2015</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>青岛增信融资担保有限公司</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>山东大集控股集团有限公司2026年面向专业投资者非公开发行低碳转型挂钩公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH7" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AK7" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL7" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>26青岛国信MTN008B</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>102683363.IB</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>青岛国信发展(集团)有限责任公司</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>山东省-青岛市</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>26青信08</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>9.93Y</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2.3710</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>中信银行股份有限公司,上海浦东发展银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>青岛国信发展(集团)有限责任公司2026年度第八期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-26</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH8" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK8" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL8" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>26唐山工业MTN002</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>102683351.IB</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>唐山工业控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>河北省-唐山市</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>26唐山工业MTN001(并购)</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2.79Y</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2.3729</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>东方证券股份有限公司,天津银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>唐山工业控股集团有限公司2026年度第二期中期票据</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-26</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>化工制造</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>化学制品</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="inlineStr">
+        <is>
+          <t>化学制品</t>
+        </is>
+      </c>
+      <c r="AH9" s="2" t="inlineStr">
+        <is>
+          <t>化学制品</t>
+        </is>
+      </c>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK9" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL9" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>26华发集团SCP007</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>012682145.IB</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0.74Y</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2.15 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>珠海华发集团有限公司</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>广东省-珠海市</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>22华发集团MTN008</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>287D</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2.3517</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>北京银行股份有限公司,上海银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>超短期融资券(SCP)</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>珠海华发集团有限公司2026年度第七期超短期融资券</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>2027-05-22</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK10" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL10" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>08-25 19:00</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>26秀业05</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>283629.SH</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2.30 ~ 3.30</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>重庆秀业投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>重庆市-秀山土家族苗族自治县</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>26秀业04</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4.56Y</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2.1131</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>西南证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>重庆秀业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL11" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>26常山纺织PPN001</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>石家庄常山纺织集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>河北省-石家庄市</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>25常山K2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2.15Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2.3546</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,中信银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>石家庄常山纺织集团有限责任公司2026年度第一期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>2028-08-26</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="inlineStr">
+        <is>
+          <t>计算机应用</t>
+        </is>
+      </c>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL12" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>08-25 19:00</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>26经金K1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>520428.SZ</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>西安经开金融控股有限公司</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>陕西省-西安市</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>25经金Z1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1.68Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2.0607</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>五矿证券有限公司,中泰证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>西安经开金融控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL13" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>26长发集团MTN002A</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>102690014.IB</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>长春市城市发展投资控股(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>吉林省-长春市</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>25长发集团MTN001B</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3.37Y</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2.0592</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>中国银河证券股份有限公司,吉林银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>长春市城市发展投资控股(集团)有限公司2026年度第二期中期票据(品种一)</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL14" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>26维信诺MTN004(科创债)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>102683339.IB</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>合肥维信诺科技有限公司</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>安徽省-合肥市</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>26维信诺MTN003(科创债)</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2.67Y</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2.1798</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>中国光大银行股份有限公司,交通银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>合肥维信诺科技有限公司2026年度第四期科技创新债券</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-26</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>电子设备制造</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>消费电子</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="inlineStr">
+        <is>
+          <t>消费电子</t>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="inlineStr">
+        <is>
+          <t>专用设备</t>
+        </is>
+      </c>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL15" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>08-25 19:30</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>26新希望MTN003(科创债)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>102683344.IB</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1.90 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>新希望集团有限公司</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>四川省-成都市</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>26新希望MTN002(科创债)</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1.79Y</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2.2020</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>招商银行股份有限公司,兴业银行股份有限公司,浙商银行股份有限公司,天津银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>民营企业</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>新希望集团有限公司2026年度第三期科技创新债券</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>2028-08-26</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="inlineStr">
+        <is>
+          <t>饲料</t>
+        </is>
+      </c>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL16" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>26鄂州城投MTN001</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>102683358.IB</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>鄂州市城市建设投资有限公司</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>湖北省-鄂州市</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>25鄂州城投MTN002</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>4.08Y</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2.0866</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>鄂州市城市建设投资有限公司2026年度第一期中期票据</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH17" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL17" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>08-25 19:00</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>26浔交02</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>283756.SH</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5+2</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>湖州市南浔区交通投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>浙江省-湖州市</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>26浔交01</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4.84Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2.1623</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>东方证券股份有限公司,华鑫证券有限责任公司,浙商证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>湖州市南浔区交通投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>2033-08-27</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>其他交运基础设施</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="inlineStr">
+        <is>
+          <t>其他交运基础设施</t>
+        </is>
+      </c>
+      <c r="AH18" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI18" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="AJ18" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AL18" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>08-25 19:00</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>26金发02</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>283808.SH</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5+5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>湖南金阳新城建设发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>湖南省-长沙市</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>26金发01</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>4.92Y+5.00Y</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2.1205</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>财信证券股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>湖南金阳新城建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-26</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="inlineStr">
+        <is>
+          <t>6.5*无效</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH19" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI19" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="AJ19" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AL19" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>26威宁投资MTN007</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>102683338.IB</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>南宁威宁投资集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>广西壮族自治区-南宁市</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>26威宁投资MTN006</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>4.97Y</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2.1079</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>上海浦东发展银行股份有限公司,浙商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>南宁威宁投资集团有限责任公司2026年度第七期中期票据</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD20" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL20" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>08-25 19:00</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>26济建02</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>283678.SH</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1.90 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>济南城市建设集团有限公司</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>24济南城建PPN001</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2.92Y</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1.7508</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>济南城市建设集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-27</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH21" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL21" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>08-25 19:00</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>26铝集K5</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>245936.SH</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>中国铝业集团有限公司</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>26铝集K2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>9.81Y</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2.0314</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司,中信证券股份有限公司,招商证券股份有限公司,平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>中央国有企业</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>中国铝业集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-27</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="inlineStr">
+        <is>
+          <t>金属和非金属矿产</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="inlineStr">
+        <is>
+          <t>常用有色金属</t>
+        </is>
+      </c>
+      <c r="AH22" s="2" t="inlineStr">
+        <is>
+          <t>工业金属</t>
+        </is>
+      </c>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL22" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>26潞安MTN006B</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>102683350.IB</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5+N</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>山西潞安矿业(集团)有限责任公司</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>山西省-长治市</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>26潞安MTN003B</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>4.88Y+N</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2.0614</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>国金证券股份有限公司,中国邮政储蓄银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>山西潞安矿业(集团)有限责任公司2026年度第六期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AL23" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>26邢台交建MTN001</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>102683334.IB</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>邢台市交通建设集团有限公司</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>河北省-邢台市</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>24邢台交建MTN003</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2.76Y</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1.9112</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,渤海银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>邢台市交通建设集团有限公司2026年度第一期中期票据</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="inlineStr">
+        <is>
+          <t>综合基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AG24" s="2" t="inlineStr">
+        <is>
+          <t>综合基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH24" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL24" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>26电网MTN025</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>102683357.IB</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>国家电网有限公司</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>26电网MTN012</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>9.67Y</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2.0356</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>中信银行股份有限公司,平安银行股份有限公司,中国建设银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>中央国有企业</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>国家电网有限公司2026年度第二十五期中期票据</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-26</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AG25" s="2" t="inlineStr">
+        <is>
+          <t>其他电力</t>
+        </is>
+      </c>
+      <c r="AH25" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL25" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>26电网MTN024</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>102683340.IB</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>国家电网有限公司</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>26电网MTN012</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>9.67Y</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>2.0356</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>兴业银行股份有限公司,浙商银行股份有限公司,中国工商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>中央国有企业</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>国家电网有限公司2026年度第二十四期中期票据</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-26</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AG26" s="2" t="inlineStr">
+        <is>
+          <t>其他电力</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL26" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>08-25 19:00</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>26甬开01</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>283790.SH</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>宁波江北开投控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>浙江省-宁波市</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>24甬开01</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>324D</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>1.5763</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>浙商证券股份有限公司,财通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>宁波市江北区国有资本投资控股有限公司</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>宁波江北开投控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AG27" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH27" s="2" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL27" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>08-25 19:00</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>26六安01</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>283829.SH</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>安徽六安新城建设投资有限公司</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>安徽省-六安市</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>24六安02</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>3.31Y</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1.8474</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>财达证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>安徽省兴泰融资担保集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>安徽六安新城建设投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF28" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL28" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>08-25 19:00</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>26城铁01</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>283762.SH</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>无锡沪宁城铁惠山站区投资开发建设有限公司</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>江苏省-无锡市</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>25城铁02</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3.87Y</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1.8769</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>天风证券股份有限公司,国联民生证券承销保荐有限公司</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>无锡沪宁城铁惠山站区投资开发建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF29" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL29" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>26心连心MTN001(科创债)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>102683346.IB</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>河南心连心化学工业集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>河南省-新乡市</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>24连云工投MTN001</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>3.09Y</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>2.0090</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,渤海银行股份有限公司,交通银行股份有限公司,中国民生银行股份有限公司,中国工商银行股份有限公司,招商银行股份有限公司,华夏银行股份有限公司,中国建设银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>民营企业</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>河南心连心化学工业集团股份有限公司2026年度第一期科技创新债券(乡村振兴)</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-26</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
+          <t>化工制造</t>
+        </is>
+      </c>
+      <c r="AF30" s="2" t="inlineStr">
+        <is>
+          <t>化学制品</t>
+        </is>
+      </c>
+      <c r="AG30" s="2" t="inlineStr">
+        <is>
+          <t>化学制品</t>
+        </is>
+      </c>
+      <c r="AH30" s="2" t="inlineStr">
+        <is>
+          <t>化学制品</t>
+        </is>
+      </c>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL30" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>08-25 19:00</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>26金瓯01</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>524984.SZ</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>光大金瓯资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>浙江省-温州市</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>25金瓯Y1</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>1.64Y+N</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>2.0902</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,光大证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>国有企业</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>光大金瓯资产管理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AF31" s="2" t="inlineStr">
+        <is>
+          <t>资产管理</t>
+        </is>
+      </c>
+      <c r="AG31" s="2" t="inlineStr">
+        <is>
+          <t>资产管理</t>
+        </is>
+      </c>
+      <c r="AH31" s="2" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL31" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN31" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/信用债发行汇总_2026-08-26.xlsx
+++ b/data/信用债发行汇总_2026-08-26.xlsx
@@ -8495,7 +8495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN31"/>
+  <dimension ref="A1:AN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8742,5332 +8742,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>08-25 18:00</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>26保利久联CP003</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>042680298.IB</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>0.49Y</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2.64 ~ 3.64</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>保利久联控股集团有限责任公司</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>贵州省-贵阳市</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>25保利久联MTN001</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>190D</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>3.6560</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>3.64</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>贵阳银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>短期融资券(CP)</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>国有企业</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>保利久联控股集团有限责任公司2026年度第三期短期融资券</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>2027-02-22</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr"/>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>化工制造</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr">
-        <is>
-          <t>化学制品</t>
-        </is>
-      </c>
-      <c r="AG2" s="2" t="inlineStr">
-        <is>
-          <t>化学制品</t>
-        </is>
-      </c>
-      <c r="AH2" s="2" t="inlineStr">
-        <is>
-          <t>化学制品</t>
-        </is>
-      </c>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK2" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL2" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>08-26 18:00</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>26威高MTN003(科创债)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>102683369.IB</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2.40 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>威高集团有限公司</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>山东省-威海市</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>26威高MTN002(科创债)</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>2.66Y</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2.7328</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>招商银行股份有限公司,青岛银行股份有限公司,中信银行股份有限公司,华夏银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>民营企业</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>威高集团有限公司2026年度第三期科技创新债券</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-27</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr"/>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr">
-        <is>
-          <t>医药制造</t>
-        </is>
-      </c>
-      <c r="AF3" s="2" t="inlineStr">
-        <is>
-          <t>医疗器械制造</t>
-        </is>
-      </c>
-      <c r="AG3" s="2" t="inlineStr">
-        <is>
-          <t>医疗器械制造</t>
-        </is>
-      </c>
-      <c r="AH3" s="2" t="inlineStr">
-        <is>
-          <t>医疗器械</t>
-        </is>
-      </c>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK3" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL3" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AN3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>08-25 19:00</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>26西经发</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>245975.SH</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2.30 ~ 3.50</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>西安经发集团有限责任公司</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>陕西省-西安市</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26经发F2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4.91Y</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2.8636</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2.87</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>天风证券股份有限公司,五矿证券有限公司</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>西安经发集团有限责任公司2026年面向专业投资者公开发行公司债券</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-27</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr"/>
-      <c r="Z4" s="2" t="inlineStr"/>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF4" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AG4" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AH4" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK4" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL4" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>08-25 18:00</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>26长发集团MTN002B</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>102690015.IB</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10Y</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2.50 ~ 3.50</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>长春市城市发展投资控股(集团)有限公司</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>吉林省-长春市</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25长发集团MTN001B</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3.37Y</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2.0592</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>中国银河证券股份有限公司,吉林银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>长春市城市发展投资控股(集团)有限公司2026年度第二期中期票据(品种二)</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>2036-08-26</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr"/>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF5" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AG5" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AH5" s="2" t="inlineStr">
-        <is>
-          <t>水务</t>
-        </is>
-      </c>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK5" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL5" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>08-26 18:00</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>26皖投集MTN004</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>102683367.IB</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>30Y</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2.30 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>安徽省投资集团控股有限公司</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>安徽省</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>25皖投集MTN004(科创债)</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19.23Y</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2.3597</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>安徽省投资集团控股有限公司2026年度第四期中期票据</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>2056-08-27</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF6" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AG6" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AH6" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK6" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL6" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AN6" s="2" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>08-25 19:00</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>26大集GT01</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>520434.SZ</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>山东大集控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>山东省-临沂市</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26大集01</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4.39Y</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2.2015</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>申万宏源证券有限公司</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>青岛增信融资担保有限公司</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>山东大集控股集团有限公司2026年面向专业投资者非公开发行低碳转型挂钩公司债券(第一期)</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-27</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr"/>
-      <c r="Z7" s="2" t="inlineStr"/>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AE7" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF7" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AG7" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AH7" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AI7" s="2" t="inlineStr"/>
-      <c r="AJ7" s="2" t="inlineStr">
-        <is>
-          <t>有担保</t>
-        </is>
-      </c>
-      <c r="AK7" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL7" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>08-25 18:00</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>26青岛国信MTN008B</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>102683363.IB</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10Y</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2.00 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>青岛国信发展(集团)有限责任公司</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>山东省-青岛市</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>26青信08</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9.93Y</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2.3710</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>中信银行股份有限公司,上海浦东发展银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>青岛国信发展(集团)有限责任公司2026年度第八期中期票据(品种二)</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t>2036-08-26</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr"/>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AD8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AE8" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF8" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AG8" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AH8" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AI8" s="2" t="inlineStr"/>
-      <c r="AJ8" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK8" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL8" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>08-25 18:00</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>26唐山工业MTN002</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>102683351.IB</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3Y</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>唐山工业控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>河北省-唐山市</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>26唐山工业MTN001(并购)</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2.79Y</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2.3729</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>东方证券股份有限公司,天津银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>唐山工业控股集团有限公司2026年度第二期中期票据</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>2029-08-26</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr">
-        <is>
-          <t>化工制造</t>
-        </is>
-      </c>
-      <c r="AF9" s="2" t="inlineStr">
-        <is>
-          <t>化学制品</t>
-        </is>
-      </c>
-      <c r="AG9" s="2" t="inlineStr">
-        <is>
-          <t>化学制品</t>
-        </is>
-      </c>
-      <c r="AH9" s="2" t="inlineStr">
-        <is>
-          <t>化学制品</t>
-        </is>
-      </c>
-      <c r="AI9" s="2" t="inlineStr"/>
-      <c r="AJ9" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK9" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL9" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>08-25 18:00</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>26华发集团SCP007</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>012682145.IB</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0.74Y</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2.15 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>珠海华发集团有限公司</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>广东省-珠海市</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22华发集团MTN008</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>287D</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2.3517</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>北京银行股份有限公司,上海银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>超短期融资券(SCP)</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>珠海华发集团有限公司2026年度第七期超短期融资券</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t>2027-05-22</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AE10" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF10" s="2" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AG10" s="2" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AH10" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AI10" s="2" t="inlineStr"/>
-      <c r="AJ10" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK10" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL10" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>08-25 19:00</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>26秀业05</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>283629.SH</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2.30 ~ 3.30</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>重庆秀业投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>重庆市-秀山土家族苗族自治县</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>26秀业04</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4.56Y</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2.1131</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>西南证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>重庆秀业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr"/>
-      <c r="Z11" s="2" t="inlineStr"/>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AE11" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF11" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AG11" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AH11" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI11" s="2" t="inlineStr"/>
-      <c r="AJ11" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK11" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL11" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>08-25 18:00</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>26常山纺织PPN001</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2Y</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>石家庄常山纺织集团有限责任公司</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>河北省-石家庄市</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>25常山K2</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2.15Y+2.00Y</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2.3546</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>国泰海通证券股份有限公司,中信银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>定向工具(PPN)</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>石家庄常山纺织集团有限责任公司2026年度第一期定向债务融资工具</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t>2028-08-26</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="inlineStr"/>
-      <c r="AE12" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF12" s="2" t="inlineStr">
-        <is>
-          <t>产业集团</t>
-        </is>
-      </c>
-      <c r="AG12" s="2" t="inlineStr">
-        <is>
-          <t>产业集团</t>
-        </is>
-      </c>
-      <c r="AH12" s="2" t="inlineStr">
-        <is>
-          <t>计算机应用</t>
-        </is>
-      </c>
-      <c r="AI12" s="2" t="inlineStr"/>
-      <c r="AJ12" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK12" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL12" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>08-25 19:00</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>26经金K1</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>520428.SZ</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>西安经开金融控股有限公司</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>陕西省-西安市</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25经金Z1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1.68Y+2.00Y</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2.0607</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>五矿证券有限公司,中泰证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>西安经开金融控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X13" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-27</t>
-        </is>
-      </c>
-      <c r="Y13" s="2" t="inlineStr"/>
-      <c r="Z13" s="2" t="inlineStr"/>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AD13" s="2" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AE13" s="2" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AF13" s="2" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AG13" s="2" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AH13" s="2" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AI13" s="2" t="inlineStr"/>
-      <c r="AJ13" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK13" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL13" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM13" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>08-25 18:00</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>26长发集团MTN002A</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>102690014.IB</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>长春市城市发展投资控股(集团)有限公司</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>吉林省-长春市</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>25长发集团MTN001B</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3.37Y</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2.0592</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>中国银河证券股份有限公司,吉林银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>长春市城市发展投资控股(集团)有限公司2026年度第二期中期票据(品种一)</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="inlineStr"/>
-      <c r="Z14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD14" s="2" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AE14" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF14" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AG14" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AH14" s="2" t="inlineStr">
-        <is>
-          <t>水务</t>
-        </is>
-      </c>
-      <c r="AI14" s="2" t="inlineStr"/>
-      <c r="AJ14" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK14" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL14" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>08-25 18:00</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>26维信诺MTN004(科创债)</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>102683339.IB</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>3Y</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1.70 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>合肥维信诺科技有限公司</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>安徽省-合肥市</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>26维信诺MTN003(科创债)</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>2.67Y</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>2.1798</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>中国光大银行股份有限公司,交通银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>合肥维信诺科技有限公司2026年度第四期科技创新债券</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X15" s="2" t="inlineStr">
-        <is>
-          <t>2029-08-26</t>
-        </is>
-      </c>
-      <c r="Y15" s="2" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
-      <c r="Z15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD15" s="2" t="inlineStr"/>
-      <c r="AE15" s="2" t="inlineStr">
-        <is>
-          <t>电子设备制造</t>
-        </is>
-      </c>
-      <c r="AF15" s="2" t="inlineStr">
-        <is>
-          <t>消费电子</t>
-        </is>
-      </c>
-      <c r="AG15" s="2" t="inlineStr">
-        <is>
-          <t>消费电子</t>
-        </is>
-      </c>
-      <c r="AH15" s="2" t="inlineStr">
-        <is>
-          <t>专用设备</t>
-        </is>
-      </c>
-      <c r="AI15" s="2" t="inlineStr"/>
-      <c r="AJ15" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK15" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL15" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>08-25 19:30</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>26新希望MTN003(科创债)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>102683344.IB</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2Y</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1.90 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>新希望集团有限公司</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>四川省-成都市</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26新希望MTN002(科创债)</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1.79Y</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2.2020</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>招商银行股份有限公司,兴业银行股份有限公司,浙商银行股份有限公司,天津银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>民营企业</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>新希望集团有限公司2026年度第三期科技创新债券</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t>2028-08-26</t>
-        </is>
-      </c>
-      <c r="Y16" s="2" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
-      <c r="Z16" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD16" s="2" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AE16" s="2" t="inlineStr">
-        <is>
-          <t>农林牧渔</t>
-        </is>
-      </c>
-      <c r="AF16" s="2" t="inlineStr">
-        <is>
-          <t>综合农林牧渔</t>
-        </is>
-      </c>
-      <c r="AG16" s="2" t="inlineStr">
-        <is>
-          <t>综合农林牧渔</t>
-        </is>
-      </c>
-      <c r="AH16" s="2" t="inlineStr">
-        <is>
-          <t>饲料</t>
-        </is>
-      </c>
-      <c r="AI16" s="2" t="inlineStr"/>
-      <c r="AJ16" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK16" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL16" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM16" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>08-25 18:00</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>26鄂州城投MTN001</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>102683358.IB</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>鄂州市城市建设投资有限公司</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>湖北省-鄂州市</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>25鄂州城投MTN002</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>4.08Y</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2.0866</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>国泰海通证券股份有限公司,申万宏源证券有限公司</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>鄂州市城市建设投资有限公司2026年度第一期中期票据</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr"/>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD17" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AE17" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF17" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AG17" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AH17" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI17" s="2" t="inlineStr"/>
-      <c r="AJ17" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK17" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL17" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>08-25 19:00</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>26浔交02</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>283756.SH</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>5+2</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>湖州市南浔区交通投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>浙江省-湖州市</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>26浔交01</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>4.84Y+2.00Y</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2.1623</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>东方证券股份有限公司,华鑫证券有限责任公司,浙商证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>湖州市南浔区交通投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X18" s="2" t="inlineStr">
-        <is>
-          <t>2033-08-27</t>
-        </is>
-      </c>
-      <c r="Y18" s="2" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
-      <c r="Z18" s="2" t="inlineStr"/>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AD18" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AE18" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF18" s="2" t="inlineStr">
-        <is>
-          <t>其他交运基础设施</t>
-        </is>
-      </c>
-      <c r="AG18" s="2" t="inlineStr">
-        <is>
-          <t>其他交运基础设施</t>
-        </is>
-      </c>
-      <c r="AH18" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI18" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-27</t>
-        </is>
-      </c>
-      <c r="AJ18" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK18" s="2" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
-      <c r="AL18" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM18" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>08-25 19:00</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>26金发02</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>283808.SH</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>5+5</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>湖南金阳新城建设发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>湖南省-长沙市</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>26金发01</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4.92Y+5.00Y</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2.1205</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>财信证券股份有限公司,中国银河证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>湖南金阳新城建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X19" s="2" t="inlineStr">
-        <is>
-          <t>2036-08-26</t>
-        </is>
-      </c>
-      <c r="Y19" s="2" t="inlineStr"/>
-      <c r="Z19" s="2" t="inlineStr"/>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD19" s="2" t="inlineStr">
-        <is>
-          <t>6.5*无效</t>
-        </is>
-      </c>
-      <c r="AE19" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF19" s="2" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AG19" s="2" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AH19" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI19" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="AJ19" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK19" s="2" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
-      <c r="AL19" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>08-25 18:00</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>26威宁投资MTN007</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>102683338.IB</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1.70 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>南宁威宁投资集团有限责任公司</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>广西壮族自治区-南宁市</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>26威宁投资MTN006</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>4.97Y</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>2.1079</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>上海浦东发展银行股份有限公司,浙商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>南宁威宁投资集团有限责任公司2026年度第七期中期票据</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X20" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="Y20" s="2" t="inlineStr"/>
-      <c r="Z20" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD20" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AE20" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF20" s="2" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AG20" s="2" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AH20" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AI20" s="2" t="inlineStr"/>
-      <c r="AJ20" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK20" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL20" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM20" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>08-25 19:00</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>26济建02</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>283678.SH</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>10Y</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1.90 ~ 2.90</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>济南城市建设集团有限公司</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>山东省-济南市</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>24济南城建PPN001</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>2.92Y</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>1.7508</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>济南城市建设集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X21" s="2" t="inlineStr">
-        <is>
-          <t>2036-08-27</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr"/>
-      <c r="Z21" s="2" t="inlineStr"/>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AE21" s="2" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AF21" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AG21" s="2" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AH21" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI21" s="2" t="inlineStr"/>
-      <c r="AJ21" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK21" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL21" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM21" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>08-25 19:00</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>26铝集K5</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>245936.SH</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>10Y</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>中国铝业集团有限公司</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>北京市</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>26铝集K2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>9.81Y</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2.0314</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>中信建投证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司,中信证券股份有限公司,招商证券股份有限公司,平安证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr"/>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>中央国有企业</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>中国铝业集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t>2036-08-27</t>
-        </is>
-      </c>
-      <c r="Y22" s="2" t="inlineStr"/>
-      <c r="Z22" s="2" t="inlineStr"/>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE22" s="2" t="inlineStr">
-        <is>
-          <t>金属和非金属矿产</t>
-        </is>
-      </c>
-      <c r="AF22" s="2" t="inlineStr">
-        <is>
-          <t>有色</t>
-        </is>
-      </c>
-      <c r="AG22" s="2" t="inlineStr">
-        <is>
-          <t>常用有色金属</t>
-        </is>
-      </c>
-      <c r="AH22" s="2" t="inlineStr">
-        <is>
-          <t>工业金属</t>
-        </is>
-      </c>
-      <c r="AI22" s="2" t="inlineStr"/>
-      <c r="AJ22" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK22" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL22" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM22" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>08-25 18:00</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>26潞安MTN006B</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>102683350.IB</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>5+N</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1.70 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>山西潞安矿业(集团)有限责任公司</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>山西省-长治市</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>26潞安MTN003B</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>4.88Y+N</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>2.0614</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr"/>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>国金证券股份有限公司,中国邮政储蓄银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>山西潞安矿业(集团)有限责任公司2026年度第六期中期票据(品种二)</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X23" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="Y23" s="2" t="inlineStr"/>
-      <c r="Z23" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD23" s="2" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AE23" s="2" t="inlineStr">
-        <is>
-          <t>化石能源</t>
-        </is>
-      </c>
-      <c r="AF23" s="2" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
-      <c r="AG23" s="2" t="inlineStr">
-        <is>
-          <t>其他煤炭</t>
-        </is>
-      </c>
-      <c r="AH23" s="2" t="inlineStr">
-        <is>
-          <t>煤炭开采</t>
-        </is>
-      </c>
-      <c r="AI23" s="2" t="inlineStr"/>
-      <c r="AJ23" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK23" s="2" t="inlineStr">
-        <is>
-          <t>永续</t>
-        </is>
-      </c>
-      <c r="AL23" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM23" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>08-25 18:00</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>26邢台交建MTN001</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>102683334.IB</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>邢台市交通建设集团有限公司</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>河北省-邢台市</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>24邢台交建MTN003</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>2.76Y</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>1.9112</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>中信证券股份有限公司,渤海银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr"/>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>邢台市交通建设集团有限公司2026年度第一期中期票据</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr"/>
-      <c r="Z24" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD24" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AE24" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF24" s="2" t="inlineStr">
-        <is>
-          <t>综合基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AG24" s="2" t="inlineStr">
-        <is>
-          <t>综合基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AH24" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI24" s="2" t="inlineStr"/>
-      <c r="AJ24" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK24" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL24" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM24" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>08-25 18:00</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>26电网MTN025</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>102683357.IB</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>10Y</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1.80 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>国家电网有限公司</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>北京市</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>26电网MTN012</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>9.67Y</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2.0356</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr"/>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>中信银行股份有限公司,平安银行股份有限公司,中国建设银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>中央国有企业</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>国家电网有限公司2026年度第二十五期中期票据</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X25" s="2" t="inlineStr">
-        <is>
-          <t>2036-08-26</t>
-        </is>
-      </c>
-      <c r="Y25" s="2" t="inlineStr"/>
-      <c r="Z25" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE25" s="2" t="inlineStr">
-        <is>
-          <t>公用事业</t>
-        </is>
-      </c>
-      <c r="AF25" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="AG25" s="2" t="inlineStr">
-        <is>
-          <t>其他电力</t>
-        </is>
-      </c>
-      <c r="AH25" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="AI25" s="2" t="inlineStr"/>
-      <c r="AJ25" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK25" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL25" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM25" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>08-25 18:00</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>26电网MTN024</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>102683340.IB</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>10Y</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1.80 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>国家电网有限公司</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>北京市</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>26电网MTN012</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>9.67Y</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>2.0356</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr"/>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>兴业银行股份有限公司,浙商银行股份有限公司,中国工商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr"/>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>中央国有企业</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>国家电网有限公司2026年度第二十四期中期票据</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t>2036-08-26</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr"/>
-      <c r="Z26" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE26" s="2" t="inlineStr">
-        <is>
-          <t>公用事业</t>
-        </is>
-      </c>
-      <c r="AF26" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="AG26" s="2" t="inlineStr">
-        <is>
-          <t>其他电力</t>
-        </is>
-      </c>
-      <c r="AH26" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="AI26" s="2" t="inlineStr"/>
-      <c r="AJ26" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK26" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL26" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM26" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>08-25 19:00</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>26甬开01</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>283790.SH</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>宁波江北开投控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>浙江省-宁波市</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>24甬开01</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>324D</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>1.5763</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr"/>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>浙商证券股份有限公司,财通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>宁波市江北区国有资本投资控股有限公司</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>宁波江北开投控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr"/>
-      <c r="Z27" s="2" t="inlineStr"/>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD27" s="2" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AE27" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF27" s="2" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AG27" s="2" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AH27" s="2" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AI27" s="2" t="inlineStr"/>
-      <c r="AJ27" s="2" t="inlineStr">
-        <is>
-          <t>有担保</t>
-        </is>
-      </c>
-      <c r="AK27" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL27" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM27" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>08-25 19:00</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>26六安01</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>283829.SH</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>安徽六安新城建设投资有限公司</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>安徽省-六安市</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>24六安02</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>3.31Y</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1.8474</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>财达证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>安徽省兴泰融资担保集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>安徽六安新城建设投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr"/>
-      <c r="Z28" s="2" t="inlineStr"/>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD28" s="2" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AE28" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF28" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AG28" s="2" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AH28" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI28" s="2" t="inlineStr"/>
-      <c r="AJ28" s="2" t="inlineStr">
-        <is>
-          <t>有担保</t>
-        </is>
-      </c>
-      <c r="AK28" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL28" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM28" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>08-25 19:00</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>26城铁01</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>283762.SH</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>5Y</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>无锡沪宁城铁惠山站区投资开发建设有限公司</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>江苏省-无锡市</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>25城铁02</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3.87Y</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>1.8769</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>天风证券股份有限公司,国联民生证券承销保荐有限公司</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr"/>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>无锡沪宁城铁惠山站区投资开发建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="X29" s="2" t="inlineStr">
-        <is>
-          <t>2031-08-27</t>
-        </is>
-      </c>
-      <c r="Y29" s="2" t="inlineStr"/>
-      <c r="Z29" s="2" t="inlineStr"/>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AD29" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AE29" s="2" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AF29" s="2" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AG29" s="2" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AH29" s="2" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AI29" s="2" t="inlineStr"/>
-      <c r="AJ29" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK29" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL29" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM29" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>08-25 18:00</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26心连心MTN001(科创债)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>102683346.IB</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>3Y</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>河南心连心化学工业集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>河南省-新乡市</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>24连云工投MTN001</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>3.09Y</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>2.0090</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>国泰海通证券股份有限公司,渤海银行股份有限公司,交通银行股份有限公司,中国民生银行股份有限公司,中国工商银行股份有限公司,招商银行股份有限公司,华夏银行股份有限公司,中国建设银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>民营企业</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>河南心连心化学工业集团股份有限公司2026年度第一期科技创新债券(乡村振兴)</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="inlineStr">
-        <is>
-          <t>2029-08-26</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
-      <c r="Z30" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AD30" s="2" t="inlineStr"/>
-      <c r="AE30" s="2" t="inlineStr">
-        <is>
-          <t>化工制造</t>
-        </is>
-      </c>
-      <c r="AF30" s="2" t="inlineStr">
-        <is>
-          <t>化学制品</t>
-        </is>
-      </c>
-      <c r="AG30" s="2" t="inlineStr">
-        <is>
-          <t>化学制品</t>
-        </is>
-      </c>
-      <c r="AH30" s="2" t="inlineStr">
-        <is>
-          <t>化学制品</t>
-        </is>
-      </c>
-      <c r="AI30" s="2" t="inlineStr"/>
-      <c r="AJ30" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK30" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL30" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM30" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>08-25 19:00</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26金瓯01</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>524984.SZ</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>3Y</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>光大金瓯资产管理有限公司</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>浙江省-温州市</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>25金瓯Y1</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>1.64Y+N</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>2.0902</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>中信建投证券股份有限公司,光大证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>国有企业</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>光大金瓯资产管理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t>2029-08-27</t>
-        </is>
-      </c>
-      <c r="Y31" s="2" t="inlineStr"/>
-      <c r="Z31" s="2" t="inlineStr"/>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AD31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AE31" s="2" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AF31" s="2" t="inlineStr">
-        <is>
-          <t>资产管理</t>
-        </is>
-      </c>
-      <c r="AG31" s="2" t="inlineStr">
-        <is>
-          <t>资产管理</t>
-        </is>
-      </c>
-      <c r="AH31" s="2" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AI31" s="2" t="inlineStr"/>
-      <c r="AJ31" s="2" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AK31" s="2" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AL31" s="2" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AM31" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN31" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/信用债发行汇总_2026-08-26.xlsx
+++ b/data/信用债发行汇总_2026-08-26.xlsx
@@ -8495,7 +8495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AN31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8742,6 +8742,5304 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>26太重MTN009(科创债)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>102683388.IB</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>3+N</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>太原重型机械集团有限公司</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>山西省-太原市</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>26太重MTN008(科创债)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>2.98Y+N</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2.6785</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,国信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>太原重型机械集团有限公司2026年度第九期科技创新债券</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>其他设备制造</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>其他专用设备</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>其他专用设备</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>专用设备</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN2" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>08-27 18:00</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>26至纯科技CP001</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>042680300.IB</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2.70 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>上海至纯洁净系统科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>24大族01</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>204D</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>1.8371</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>上海农村商业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>短期融资券(CP)</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>民营企业</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>上海至纯洁净系统科技股份有限公司2026年度第一期短期融资券</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>2027-08-28</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>其他设备制造</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>其他专用设备</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>其他专用设备</t>
+        </is>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>专用设备</t>
+        </is>
+      </c>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK3" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL3" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>26晋旅01</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>283807.SH</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>山西省文化旅游投资控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>山西省-太原市</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>25晋旅01</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4.29Y</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2.4247</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,申万宏源证券有限公司,平安证券股份有限公司,东方证券股份有限公司,财信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>山西省文化旅游投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>旅游综合</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL4" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>26广电河北MTN002</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>102683397.IB</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>中国广电河北网络股份有限公司</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>河北省-石家庄市</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>26河北广电MTN001</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2.93Y</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2.4472</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,河北银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>国有企业</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>中国广电河北网络股份有限公司2026年度第二期中期票据</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>传媒</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>广电</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr">
+        <is>
+          <t>广电</t>
+        </is>
+      </c>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>文化传媒</t>
+        </is>
+      </c>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK5" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL5" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN5" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>26麒麟02</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>283782.SH</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2.50 ~ 3.50</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>曲靖市麒麟区城乡建设投资(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>云南省-曲靖市</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>24阜阳债</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2.65Y</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2.0028</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>太平洋证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>曲靖市麒麟区城乡建设投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK6" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL6" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>08-27 18:00</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>26焦作投资MTN002B</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>102690018.IB</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>焦作市投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>河南省-焦作市</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>26焦作投资MTN001</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4.67Y</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2.0813</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>广发证券股份有限公司,交通银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>焦作市投资集团有限公司2026年度第二期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>2033-08-28</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH7" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK7" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL7" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN7" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>26江铜股份MTN003B(并购)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>102683390.IB</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15Y</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2.13 ~ 2.33</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>江西铜业股份有限公司</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>江西省-鹰潭市</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>26江铜股份MTN002B(并购)</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>14.97Y</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2.3289</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>中国建设银行股份有限公司,上海浦东发展银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>江西铜业股份有限公司2026年度第三期中期票据(并购)(品种二)</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>2041-08-27</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>金属和非金属矿产</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="inlineStr">
+        <is>
+          <t>常用有色金属</t>
+        </is>
+      </c>
+      <c r="AH8" s="2" t="inlineStr">
+        <is>
+          <t>工业金属</t>
+        </is>
+      </c>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK8" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL8" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN8" s="2" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>08-26 17:00</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>26纳兴01</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>283637.SH</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>四川纳兴实业集团有限公司</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>四川省-泸州市</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>25纳兴02</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1.77Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2.1100</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>四川纳兴实业集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH9" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI9" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK9" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AL9" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>26冀中能源MTN017B</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>102683375.IB</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3+N</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2.10 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>冀中能源集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>河北省-邢台市</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>26冀中能源MTN015B</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2.96Y+N</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2.3267</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>冀中能源集团有限责任公司2026年度第十七期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK10" s="2" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AL10" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN10" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>26资阳国资PPN001</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>资阳发展投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>四川省-资阳市</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>25资阳国资PPN001</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4.32Y</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2.1603</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>平安证券股份有限公司,国信证券股份有限公司,重庆银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>资阳市投资控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>资阳发展投资集团有限公司2026年度第一期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL11" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>26沪开02</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>245850.SH</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>上海城开(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>25沪开04</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4.31Y</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2.1470</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>上海城开(集团)有限公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-28</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr">
+        <is>
+          <t>综合地产开发</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL12" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>26水发02</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>283824.SH</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>水发集团有限公司</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>26水发01</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2.67Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2.1543</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>长江证券股份有限公司,兴业证券股份有限公司,广发证券股份有限公司,德邦证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>水发集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>其他基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="inlineStr">
+        <is>
+          <t>其他基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI13" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="AJ13" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AL13" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>26渝空01</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>283711.SH</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>重庆空港新城开发建设有限公司</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>重庆市-两江新区</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>24渝空02</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3.30Y</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1.9868</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>西南证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>重庆临空开发投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>重庆空港新城开发建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL14" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>26江铜股份MTN003A(并购)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>102683389.IB</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1.95 ~ 2.15</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>江西铜业股份有限公司</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>江西省-鹰潭市</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>26江铜股份MTN002A(并购)</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>9.97Y</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2.1502</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>中国建设银行股份有限公司,上海浦东发展银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>江西铜业股份有限公司2026年度第三期中期票据(并购)(品种一)</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-27</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>金属和非金属矿产</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="inlineStr">
+        <is>
+          <t>常用有色金属</t>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="inlineStr">
+        <is>
+          <t>工业金属</t>
+        </is>
+      </c>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL15" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN15" s="2" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>26滕州国资MTN002B</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>102683385.IB</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>滕州市城市国有资产经营有限公司</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>山东省-枣庄市</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>26滕州国资MTN001</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4.37Y</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2.1109</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,南京银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>滕州市城市国有资产经营有限公司2026年度第二期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL16" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN16" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>26中创新航MTN003(科创债)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>102683380.IB</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>中创新航科技集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>江苏省-常州市</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>26中创新航MTN002(科创债)</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2.67Y</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2.1335</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>上海浦东发展银行股份有限公司,华夏银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>中创新航科技集团股份有限公司2026年度第三期绿色科技创新债券</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr">
+        <is>
+          <t>电力设备制造</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>其他电力设备</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="inlineStr">
+        <is>
+          <t>其他电力设备</t>
+        </is>
+      </c>
+      <c r="AH17" s="2" t="inlineStr">
+        <is>
+          <t>电源设备</t>
+        </is>
+      </c>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL17" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>26重庆渝开MTN001</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>102683372.IB</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2+2+1</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>重庆渝开发股份有限公司</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>25宏洋03</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2.06Y</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2.0287</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>兴业银行股份有限公司,中国民生银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>中证信用融资担保有限公司</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>重庆渝开发股份有限公司2026年度第一期中期票据</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="inlineStr">
+        <is>
+          <t>住宅楼房</t>
+        </is>
+      </c>
+      <c r="AH18" s="2" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AI18" s="2" t="inlineStr">
+        <is>
+          <t>2028-08-27</t>
+        </is>
+      </c>
+      <c r="AJ18" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AL18" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN18" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>08-27 18:00</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>26焦作投资MTN002A</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>102690017.IB</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>焦作市投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>河南省-焦作市</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>26焦作投资MTN001</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>4.67Y</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2.0813</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>广发证券股份有限公司,交通银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>焦作市投资集团有限公司2026年度第二期中期票据(品种一)</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-28</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH19" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL19" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN19" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>26威海02</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>283692.SH</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>威海城市投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>山东省-威海市</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>26威海01</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>4.76Y</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2.0955</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>威海城市投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-28</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AD20" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL20" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>26浙资运营MTN003(科创债)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>102683394.IB</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>浙江省国有资本运营有限公司</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>浙江省</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>26浙资K1</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>9.40Y</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2.0707</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>杭州银行股份有限公司,上海浦东发展银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>浙江省国有资本运营有限公司2026年度第三期科技创新债券</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-27</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AD21" s="2" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH21" s="2" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL21" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN21" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>26沪开01</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>245849.SH</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>上海城开(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>25沪开03</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2.31Y</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2.0464</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>上海城开(集团)有限公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-28</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="inlineStr">
+        <is>
+          <t>综合地产开发</t>
+        </is>
+      </c>
+      <c r="AH22" s="2" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL22" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>26沪港务MTN010</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>102683379.IB</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>上海国际港务(集团)股份有限公司</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>26沪港务MTN005</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>9.68Y</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2.0677</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>上海银行股份有限公司,中信银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>上海国际港务(集团)股份有限公司2026年度第十期中期票据</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-27</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL23" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>26沪港务MTN011</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>102683391.IB</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>上海国际港务(集团)股份有限公司</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>26沪港务MTN005</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>9.68Y</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2.0677</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>招商银行股份有限公司,中国建设银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>上海国际港务(集团)股份有限公司2026年度第十一期中期票据</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-27</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AG24" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AH24" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL24" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>26冀中能源MTN017A</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>102683374.IB</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2+N</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>冀中能源集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>河北省-邢台市</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>25冀中能源MTN006</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1.81Y+N</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2.0454</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>冀中能源集团有限责任公司2026年度第十七期中期票据(品种一)</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>2028-08-27</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AG25" s="2" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AH25" s="2" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AL25" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN25" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>26电网MTN026</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>102683382.IB</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>国家电网有限公司</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>26电网MTN012</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>9.67Y</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>2.0374</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>中国民生银行股份有限公司,中国银行股份有限公司,交通银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>中央国有企业</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>国家电网有限公司2026年度第二十六期中期票据</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-27</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AG26" s="2" t="inlineStr">
+        <is>
+          <t>其他电力</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL26" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>26武夷投资MTN004</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>102683402.IB</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>南平武夷新区投资开发集团有限公司</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>福建省-南平市</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>26武夷投资MTN003</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>4.87Y</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>2.0449</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,兴业证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>南平武夷新区投资开发集团有限公司2026年度第四期中期票据</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AG27" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH27" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL27" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>26深铁08</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>520437.SZ</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>5+2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>深圳市地铁集团有限公司</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>广东省-深圳市</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>26深铁06</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>4.96Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>2.0015</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>中国国际金融股份有限公司,华泰联合证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)(品种二)</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>2033-08-28</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AF28" s="2" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="inlineStr">
+        <is>
+          <t>公交</t>
+        </is>
+      </c>
+      <c r="AI28" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-28</t>
+        </is>
+      </c>
+      <c r="AJ28" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AL28" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>中煤能K8</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>245977.SH</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>中国中煤能源集团有限公司</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>中煤能K6</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>9.20Y</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1.9715</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司,中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>中央国有企业</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>中国中煤能源集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)(品种二)</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-28</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AF29" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>煤炭采掘</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL29" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>26泰山04</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>283763.SH</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>泰安市财金产业发展有限公司</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>山东省-泰安市</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>26泰山01</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2.66Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>1.9911</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,光大证券股份有限公司,平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>泰安市财金产业发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AF30" s="2" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AG30" s="2" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AH30" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AI30" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="AJ30" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AL30" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>26鹿工01</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>283550.SH</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>温州市鹿城区工业发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>浙江省-温州市</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>26德庆01</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>4.98Y</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>2.1510</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>东方证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>中证信用融资担保有限公司</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>温州市鹿城区工业发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-28</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AF31" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AG31" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH31" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AL31" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AM31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN31" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/信用债发行汇总_2026-08-26.xlsx
+++ b/data/信用债发行汇总_2026-08-26.xlsx
@@ -10,6 +10,7 @@
     <sheet name="当日新增_2026-08-26" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="汇总" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="新债预测≥2.0(全市场)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="新债预测≥2.0(全市场)汇总" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14043,4 +14044,9949 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AO54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="8" customWidth="1" min="37" max="37"/>
+    <col width="8" customWidth="1" min="38" max="38"/>
+    <col width="8" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="8" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>首次提取日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>截标时间</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>债券简称</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>债券代码</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>发行期限</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>计划发行(亿)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>投标区间(%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>票面利率(%)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>发行人</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>相似二级券</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>相似二级剩余期限</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>相似二级估值</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>YY评分</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>新债预测</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>主体评级</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>债项评级</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>主承销商</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>担保人</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>债券类型</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>发行人类型</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>交易市场</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>债券全称</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>募集方式</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>实际到期日</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>到期日休市情况</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>上市日</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>公告日</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>缴款日</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>板块分类</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>DM评分</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>DM一级行业</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>DM二级行业</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>DM三级行业</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>申万行业</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>行权日</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>是否有担保</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>条款</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>偿付顺序</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>发行截止日</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>团费(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>26太重MTN009(科创债)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>102683388.IB</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>3+N</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>太原重型机械集团有限公司</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>山西省-太原市</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>26太重MTN008(科创债)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2.98Y+N</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2.6785</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,国信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>太原重型机械集团有限公司2026年度第九期科技创新债券</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>其他设备制造</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>其他专用设备</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>其他专用设备</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>专用设备</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO2" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>08-27 18:00</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>26至纯科技CP001</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>042680300.IB</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2.70 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>上海至纯洁净系统科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>24大族01</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>204D</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>1.8371</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>上海农村商业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>短期融资券(CP)</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>民营企业</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>上海至纯洁净系统科技股份有限公司2026年度第一期短期融资券</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>2027-08-28</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>其他设备制造</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>其他专用设备</t>
+        </is>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>其他专用设备</t>
+        </is>
+      </c>
+      <c r="AI3" s="2" t="inlineStr">
+        <is>
+          <t>专用设备</t>
+        </is>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AK3" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL3" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM3" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AO3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>26晋旅01</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>283807.SH</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>山西省文化旅游投资控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>山西省-太原市</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>25晋旅01</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4.29Y</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2.4247</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,申万宏源证券有限公司,平安证券股份有限公司,东方证券股份有限公司,财信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>山西省文化旅游投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>旅游综合</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL4" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM4" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>26广电河北MTN002</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>102683397.IB</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>中国广电河北网络股份有限公司</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>河北省-石家庄市</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>26河北广电MTN001</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2.93Y</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2.4472</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,河北银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>国有企业</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>中国广电河北网络股份有限公司2026年度第二期中期票据</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>传媒</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr">
+        <is>
+          <t>广电</t>
+        </is>
+      </c>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>广电</t>
+        </is>
+      </c>
+      <c r="AI5" s="2" t="inlineStr">
+        <is>
+          <t>文化传媒</t>
+        </is>
+      </c>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL5" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM5" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO5" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>26麒麟02</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>283782.SH</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2.50 ~ 3.50</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>曲靖市麒麟区城乡建设投资(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>云南省-曲靖市</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>24阜阳债</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2.65Y</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2.0028</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>太平洋证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>曲靖市麒麟区城乡建设投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AI6" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL6" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM6" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>08-27 18:00</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>26焦作投资MTN002B</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>102690018.IB</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>焦作市投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>河南省-焦作市</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>26焦作投资MTN001</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4.67Y</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2.0813</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>广发证券股份有限公司,交通银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>焦作市投资集团有限公司2026年度第二期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>2033-08-28</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH7" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AI7" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AK7" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL7" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM7" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AO7" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>26江铜股份MTN003B(并购)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>102683390.IB</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15Y</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2.13 ~ 2.33</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>江西铜业股份有限公司</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>江西省-鹰潭市</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>26江铜股份MTN002B(并购)</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>14.97Y</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2.3289</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>中国建设银行股份有限公司,上海浦东发展银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>江西铜业股份有限公司2026年度第三期中期票据(并购)(品种二)</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>2041-08-27</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>金属和非金属矿产</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="AH8" s="2" t="inlineStr">
+        <is>
+          <t>常用有色金属</t>
+        </is>
+      </c>
+      <c r="AI8" s="2" t="inlineStr">
+        <is>
+          <t>工业金属</t>
+        </is>
+      </c>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL8" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM8" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO8" s="2" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>08-26 17:00</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>26纳兴01</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>283637.SH</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>四川纳兴实业集团有限公司</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>四川省-泸州市</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>25纳兴02</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1.77Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2.1100</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>四川纳兴实业集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH9" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AI9" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="AK9" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL9" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AM9" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>26冀中能源MTN017B</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>102683375.IB</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3+N</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2.10 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>冀中能源集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>河北省-邢台市</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>26冀中能源MTN015B</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2.96Y+N</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2.3267</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>冀中能源集团有限责任公司2026年度第十七期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AI10" s="2" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AK10" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL10" s="2" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AM10" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO10" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>26资阳国资PPN001</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>资阳发展投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>四川省-资阳市</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>25资阳国资PPN001</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4.32Y</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2.1603</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>平安证券股份有限公司,国信证券股份有限公司,重庆银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>资阳市投资控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>资阳发展投资集团有限公司2026年度第一期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AI11" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AK11" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AL11" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM11" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>26沪开02</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>245850.SH</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>上海城开(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>25沪开04</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4.31Y</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2.1470</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>上海城开(集团)有限公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-28</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="inlineStr">
+        <is>
+          <t>综合地产开发</t>
+        </is>
+      </c>
+      <c r="AI12" s="2" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL12" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM12" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>26水发02</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>283824.SH</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>水发集团有限公司</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>26水发01</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2.67Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2.1543</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>长江证券股份有限公司,兴业证券股份有限公司,广发证券股份有限公司,德邦证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>水发集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="inlineStr">
+        <is>
+          <t>其他基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="inlineStr">
+        <is>
+          <t>其他基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AI13" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ13" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL13" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AM13" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>26渝空01</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>283711.SH</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>重庆空港新城开发建设有限公司</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>重庆市-两江新区</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>24渝空02</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3.30Y</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1.9868</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>西南证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>重庆临空开发投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>重庆空港新城开发建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AI14" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ14" s="2" t="inlineStr"/>
+      <c r="AK14" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AL14" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM14" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>26江铜股份MTN003A(并购)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>102683389.IB</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1.95 ~ 2.15</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>江西铜业股份有限公司</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>江西省-鹰潭市</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>26江铜股份MTN002A(并购)</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>9.97Y</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2.1502</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>中国建设银行股份有限公司,上海浦东发展银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>江西铜业股份有限公司2026年度第三期中期票据(并购)(品种一)</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-27</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>金属和非金属矿产</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="inlineStr">
+        <is>
+          <t>常用有色金属</t>
+        </is>
+      </c>
+      <c r="AI15" s="2" t="inlineStr">
+        <is>
+          <t>工业金属</t>
+        </is>
+      </c>
+      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AK15" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL15" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM15" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO15" s="2" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>26滕州国资MTN002B</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>102683385.IB</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>滕州市城市国有资产经营有限公司</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>山东省-枣庄市</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>26滕州国资MTN001</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4.37Y</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2.1109</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,南京银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>滕州市城市国有资产经营有限公司2026年度第二期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AI16" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ16" s="2" t="inlineStr"/>
+      <c r="AK16" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL16" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM16" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO16" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>26中创新航MTN003(科创债)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>102683380.IB</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>中创新航科技集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>江苏省-常州市</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>26中创新航MTN002(科创债)</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2.67Y</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2.1335</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>上海浦东发展银行股份有限公司,华夏银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>中创新航科技集团股份有限公司2026年度第三期绿色科技创新债券</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>电力设备制造</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="inlineStr">
+        <is>
+          <t>其他电力设备</t>
+        </is>
+      </c>
+      <c r="AH17" s="2" t="inlineStr">
+        <is>
+          <t>其他电力设备</t>
+        </is>
+      </c>
+      <c r="AI17" s="2" t="inlineStr">
+        <is>
+          <t>电源设备</t>
+        </is>
+      </c>
+      <c r="AJ17" s="2" t="inlineStr"/>
+      <c r="AK17" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL17" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM17" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>26重庆渝开MTN001</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>102683372.IB</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2+2+1</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>重庆渝开发股份有限公司</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>25宏洋03</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2.06Y</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2.0287</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>兴业银行股份有限公司,中国民生银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>中证信用融资担保有限公司</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>重庆渝开发股份有限公司2026年度第一期中期票据</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AH18" s="2" t="inlineStr">
+        <is>
+          <t>住宅楼房</t>
+        </is>
+      </c>
+      <c r="AI18" s="2" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AJ18" s="2" t="inlineStr">
+        <is>
+          <t>2028-08-27</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AL18" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AM18" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO18" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>08-27 18:00</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>26焦作投资MTN002A</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>102690017.IB</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>焦作市投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>河南省-焦作市</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>26焦作投资MTN001</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>4.67Y</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2.0813</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>广发证券股份有限公司,交通银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>焦作市投资集团有限公司2026年度第二期中期票据(品种一)</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-28</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH19" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AI19" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ19" s="2" t="inlineStr"/>
+      <c r="AK19" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL19" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM19" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AO19" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>26威海02</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>283692.SH</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>威海城市投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>山东省-威海市</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>26威海01</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4.76Y</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2.0955</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>威海城市投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-28</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD20" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AI20" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ20" s="2" t="inlineStr"/>
+      <c r="AK20" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL20" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM20" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>26浙资运营MTN003(科创债)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>102683394.IB</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>浙江省国有资本运营有限公司</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>浙江省</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>26浙资K1</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>9.40Y</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2.0707</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>杭州银行股份有限公司,上海浦东发展银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>浙江省国有资本运营有限公司2026年度第三期科技创新债券</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-27</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD21" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH21" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AI21" s="2" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="AJ21" s="2" t="inlineStr"/>
+      <c r="AK21" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL21" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM21" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO21" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>26沪开01</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>245849.SH</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>上海城开(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>25沪开03</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2.31Y</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2.0464</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>上海城开(集团)有限公司2026年面向专业投资者公开发行公司债券(第一期)(品种一)</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-28</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AH22" s="2" t="inlineStr">
+        <is>
+          <t>综合地产开发</t>
+        </is>
+      </c>
+      <c r="AI22" s="2" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AJ22" s="2" t="inlineStr"/>
+      <c r="AK22" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL22" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM22" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>26沪港务MTN010</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>102683379.IB</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>上海国际港务(集团)股份有限公司</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>26沪港务MTN005</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>9.68Y</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2.0677</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>上海银行股份有限公司,中信银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>上海国际港务(集团)股份有限公司2026年度第十期中期票据</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-27</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AI23" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AJ23" s="2" t="inlineStr"/>
+      <c r="AK23" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL23" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM23" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>26沪港务MTN011</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>102683391.IB</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>上海国际港务(集团)股份有限公司</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>26沪港务MTN005</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>9.68Y</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2.0677</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>招商银行股份有限公司,中国建设银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>上海国际港务(集团)股份有限公司2026年度第十一期中期票据</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-27</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG24" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AH24" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AI24" s="2" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AJ24" s="2" t="inlineStr"/>
+      <c r="AK24" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL24" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM24" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>26冀中能源MTN017A</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>102683374.IB</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2+N</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>冀中能源集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>河北省-邢台市</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>25冀中能源MTN006</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1.81Y+N</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2.0454</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>冀中能源集团有限责任公司2026年度第十七期中期票据(品种一)</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>2028-08-27</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AG25" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AH25" s="2" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AI25" s="2" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AJ25" s="2" t="inlineStr"/>
+      <c r="AK25" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL25" s="2" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AM25" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO25" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>26电网MTN026</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>102683382.IB</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>国家电网有限公司</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>26电网MTN012</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>9.67Y</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2.0374</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>中国民生银行股份有限公司,中国银行股份有限公司,交通银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>中央国有企业</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>国家电网有限公司2026年度第二十六期中期票据</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-27</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AG26" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="inlineStr">
+        <is>
+          <t>其他电力</t>
+        </is>
+      </c>
+      <c r="AI26" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AJ26" s="2" t="inlineStr"/>
+      <c r="AK26" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL26" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM26" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>26武夷投资MTN004</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>102683402.IB</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>南平武夷新区投资开发集团有限公司</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>福建省-南平市</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>26武夷投资MTN003</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>4.87Y</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2.0449</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,兴业证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>南平武夷新区投资开发集团有限公司2026年度第四期中期票据</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG27" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH27" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AI27" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ27" s="2" t="inlineStr"/>
+      <c r="AK27" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL27" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM27" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>26深铁08</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>520437.SZ</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>5+2</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>深圳市地铁集团有限公司</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>广东省-深圳市</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>26深铁06</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>4.96Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2.0015</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>中国国际金融股份有限公司,华泰联合证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)(品种二)</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>2033-08-28</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF28" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AI28" s="2" t="inlineStr">
+        <is>
+          <t>公交</t>
+        </is>
+      </c>
+      <c r="AJ28" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-28</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL28" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AM28" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>中煤能K8</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>245977.SH</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>中国中煤能源集团有限公司</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>中煤能K6</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>9.20Y</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1.9715</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司,中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>中央国有企业</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>中国中煤能源集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)(品种二)</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-28</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF29" s="2" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="inlineStr">
+        <is>
+          <t>煤炭采掘</t>
+        </is>
+      </c>
+      <c r="AI29" s="2" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AJ29" s="2" t="inlineStr"/>
+      <c r="AK29" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL29" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM29" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>26泰山04</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>283763.SH</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>泰安市财金产业发展有限公司</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>山东省-泰安市</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>26泰山01</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>2.66Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>1.9911</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,光大证券股份有限公司,平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>泰安市财金产业发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AG30" s="2" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AH30" s="2" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AI30" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AJ30" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL30" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AM30" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>08-26 18:00</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>26鹿工01</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>283550.SH</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>温州市鹿城区工业发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>浙江省-温州市</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>26德庆01</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>4.98Y</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2.1510</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>东方证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>中证信用融资担保有限公司</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>温州市鹿城区工业发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-28</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AG31" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH31" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AI31" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AJ31" s="2" t="inlineStr"/>
+      <c r="AK31" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AL31" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM31" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>08-24 18:00</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>26济南建工MTN001</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>102683324.IB</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>2+N</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>3.00 ~ 4.00</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>济南建工集团有限公司</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>25济南建工MTN001A</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>1.88Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2.2233</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>济南建工集团有限公司2026年度第一期中期票据</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>2028-08-25</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AF32" s="2" t="inlineStr">
+        <is>
+          <t>建筑施工</t>
+        </is>
+      </c>
+      <c r="AG32" s="2" t="inlineStr">
+        <is>
+          <t>房屋建筑</t>
+        </is>
+      </c>
+      <c r="AH32" s="2" t="inlineStr">
+        <is>
+          <t>其他房建</t>
+        </is>
+      </c>
+      <c r="AI32" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ32" s="2" t="inlineStr"/>
+      <c r="AK32" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL32" s="2" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AM32" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO32" s="2" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>08-24 19:00</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>26百色02</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>283749.SH</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2.30 ~ 3.50</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>广西百色试验区发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>广西壮族自治区-百色市</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>26百色01</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>4.80Y</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2.6510</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>天风证券股份有限公司,国海证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>广西百色城市产业发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>广西百色试验区发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AF33" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG33" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AH33" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AI33" s="2" t="inlineStr">
+        <is>
+          <t>贸易</t>
+        </is>
+      </c>
+      <c r="AJ33" s="2" t="inlineStr"/>
+      <c r="AK33" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AL33" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM33" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>08-24 19:00</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>26沂发02</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>283786.SH</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2.50 ~ 3.50</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>新沂经济开发区建设发展有限公司</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>江苏省-徐州市</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>24沂发03</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>3.00Y</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>1.8412</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>申港证券股份有限公司,国泰海通证券股份有限公司,国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>江苏钟吾城乡投资发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>新沂经济开发区建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>2033-08-25</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AE34" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AF34" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG34" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AH34" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AI34" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ34" s="2" t="inlineStr"/>
+      <c r="AK34" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AL34" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM34" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>08-24 19:00</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>26寿光01</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>520439.SZ</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2.30 ~ 3.30</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>寿光市惠农新农村建设投资开发有限公司</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>山东省-潍坊市</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>25寿光04</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>3.96Y</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2.2840</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>财达证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>寿光市惠农新农村建设投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AE35" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AF35" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG35" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH35" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AI35" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ35" s="2" t="inlineStr"/>
+      <c r="AK35" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL35" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM35" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>08-24 18:00</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>26太湖新城MTN008</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>102683302.IB</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>无锡市太湖新城发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>江苏省-无锡市</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>26太湖新城MTN007</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>9.99Y</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2.3777</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>中国民生银行股份有限公司,中国光大银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>无锡市太湖新城发展集团有限公司2026年度第八期中期票据</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-25</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AE36" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AF36" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG36" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH36" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AI36" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ36" s="2" t="inlineStr"/>
+      <c r="AK36" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL36" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM36" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO36" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>08-24 18:00</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>26太湖新城MTN009</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>102683316.IB</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>无锡市太湖新城发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>江苏省-无锡市</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>26太湖新城MTN007</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>9.99Y</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2.3777</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>华夏银行股份有限公司,中国建设银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>无锡市太湖新城发展集团有限公司2026年度第九期中期票据</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-25</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AE37" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AF37" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG37" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH37" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AI37" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ37" s="2" t="inlineStr"/>
+      <c r="AK37" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL37" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM37" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO37" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>08-24 18:00</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>26德阳经开MTN001A</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>102683295.IB</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>德阳经开区发展(控股)集团有限公司</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>四川省-德阳市</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>25德阳经开MTN001</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>3.52Y</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2.2598</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>长江证券股份有限公司,成都银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>双城(重庆)信用增进股份有限公司</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>德阳经开区发展(控股)集团有限公司2026年度第一期中期票据(品种一)</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AE38" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AF38" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG38" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AH38" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AI38" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ38" s="2" t="inlineStr"/>
+      <c r="AK38" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AL38" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM38" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>08-24 18:00</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>26德阳经开MTN001B</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>102683296.IB</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>德阳经开区发展(控股)集团有限公司</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>四川省-德阳市</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>25德阳经开MTN001</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>3.52Y</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2.2598</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>长江证券股份有限公司,成都银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>重庆三峡融资担保集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>德阳经开区发展(控股)集团有限公司2026年度第一期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AE39" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AF39" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG39" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AH39" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AI39" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ39" s="2" t="inlineStr"/>
+      <c r="AK39" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AL39" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM39" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>08-24 18:00</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>26新疆城建MTN002</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>102690013.IB</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1.90 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>新疆城建(集团)股份有限公司</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>新疆维吾尔自治区-乌鲁木齐市</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>26新疆城建MTN001</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>1.83Y</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2.1651</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>中国国际金融股份有限公司</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>新疆城建(集团)股份有限公司2026年度第二期中期票据</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-25</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE40" s="2" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="AF40" s="2" t="inlineStr">
+        <is>
+          <t>建筑施工</t>
+        </is>
+      </c>
+      <c r="AG40" s="2" t="inlineStr">
+        <is>
+          <t>综合建筑施工</t>
+        </is>
+      </c>
+      <c r="AH40" s="2" t="inlineStr">
+        <is>
+          <t>综合建筑施工</t>
+        </is>
+      </c>
+      <c r="AI40" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ40" s="2" t="inlineStr"/>
+      <c r="AK40" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL40" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM40" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>08-24 18:00</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>26上饶城投PPN003B</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>上饶市城市建设投资开发集团有限公司</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>江西省-上饶市</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>24上饶08</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>5.05Y</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2.0540</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>广发证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>上饶市城市建设投资开发集团有限公司2026年度第三期定向债务融资工具(品种二)</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>2033-08-25</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AE41" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF41" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AG41" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH41" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AI41" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ41" s="2" t="inlineStr"/>
+      <c r="AK41" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL41" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM41" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO41" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>08-24 19:00</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>26渝旅03</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>283778.SH</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>重庆文化旅游集团有限公司</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>26渝旅01</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>4.89Y</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2.2744</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,西南证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>华中(武汉)融资担保股份有限公司</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>重庆文化旅游集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AE42" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AF42" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG42" s="2" t="inlineStr">
+        <is>
+          <t>其他基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH42" s="2" t="inlineStr">
+        <is>
+          <t>其他基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AI42" s="2" t="inlineStr">
+        <is>
+          <t>旅游综合</t>
+        </is>
+      </c>
+      <c r="AJ42" s="2" t="inlineStr"/>
+      <c r="AK42" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AL42" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM42" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>08-24 19:00</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>26桂资01</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>283760.SH</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>广西资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>广西壮族自治区-南宁市</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>25桂金01</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>1.76Y</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2.1654</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>华创证券有限责任公司,国海证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>广西资产管理有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-26</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AE43" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF43" s="2" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AG43" s="2" t="inlineStr">
+        <is>
+          <t>资产管理</t>
+        </is>
+      </c>
+      <c r="AH43" s="2" t="inlineStr">
+        <is>
+          <t>资产管理</t>
+        </is>
+      </c>
+      <c r="AI43" s="2" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AJ43" s="2" t="inlineStr"/>
+      <c r="AK43" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL43" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM43" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>08-24 18:00</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>26临沂投资PPN001</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>临沂投资发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>山东省-临沂市</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>24临沂投资PPN002</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>2.91Y</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2.0932</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>长城证券股份有限公司,青岛银行股份有限公司,申万宏源证券有限公司,中信证券股份有限公司,东方证券股份有限公司,广发证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>临沂投资发展集团有限公司2026年度第一期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AE44" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AF44" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AG44" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH44" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AI44" s="2" t="inlineStr">
+        <is>
+          <t>钢铁</t>
+        </is>
+      </c>
+      <c r="AJ44" s="2" t="inlineStr"/>
+      <c r="AK44" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL44" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM44" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>08-24 18:00</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>26济南高新MTN007B</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>102683304.IB</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>5+N</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>济南高新控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>26济南高新MTN001B</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>4.44Y+N</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>2.0834</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,平安银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>济南高新控股集团有限公司2026年度第七期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE45" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF45" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG45" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AH45" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AI45" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ45" s="2" t="inlineStr"/>
+      <c r="AK45" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL45" s="2" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AM45" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>08-24 18:00</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>26中铁十一MTN002B</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>102683318.IB</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>5+N</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>中铁十一局集团有限公司</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>湖北省-武汉市</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>26中铁十一MTN001B</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>4.97Y+N</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2.1286</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>国有企业</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>中铁十一局集团有限公司2026年度第二期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE46" s="2" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="AF46" s="2" t="inlineStr">
+        <is>
+          <t>建筑施工</t>
+        </is>
+      </c>
+      <c r="AG46" s="2" t="inlineStr">
+        <is>
+          <t>专业工程</t>
+        </is>
+      </c>
+      <c r="AH46" s="2" t="inlineStr">
+        <is>
+          <t>市政路桥</t>
+        </is>
+      </c>
+      <c r="AI46" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ46" s="2" t="inlineStr"/>
+      <c r="AK46" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL46" s="2" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AM46" s="2" t="inlineStr">
+        <is>
+          <t>次级债权</t>
+        </is>
+      </c>
+      <c r="AN46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO46" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>08-24 19:00</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>26安租Y6</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>245894.SH</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>3+N</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>平安国际融资租赁有限公司</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>26安租Y4</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>1.64Y+N</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>1.9643</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>平安证券股份有限公司,中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>民营企业</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>平安国际融资租赁有限公司2026年面向专业投资者公开发行可续期公司债券(第三期)</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>2029-08-26</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AE47" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF47" s="2" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AG47" s="2" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AH47" s="2" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AI47" s="2" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AJ47" s="2" t="inlineStr"/>
+      <c r="AK47" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL47" s="2" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AM47" s="2" t="inlineStr">
+        <is>
+          <t>次级债权</t>
+        </is>
+      </c>
+      <c r="AN47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>08-24 18:00</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>26上饶城投PPN003A</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>上饶市城市建设投资开发集团有限公司</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>江西省-上饶市</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>24上饶07</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>5.00Y</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2.0440</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>广发证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>上饶市城市建设投资开发集团有限公司2026年度第三期定向债务融资工具(品种一)</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AE48" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF48" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AG48" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH48" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AI48" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ48" s="2" t="inlineStr"/>
+      <c r="AK48" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL48" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM48" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO48" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>08-24 18:00</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>26荆门城建MTN002</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>102683301.IB</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>5+5</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>湖北荆门城建集团有限公司</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>湖北省-荆门市</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>25荆门城建MTN005</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>3.82Y</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2.0171</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>平安证券股份有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>湖北荆门城建集团有限公司2026年度第二期中期票据</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-25</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AE49" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AF49" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG49" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AH49" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AI49" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ49" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="AK49" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL49" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AM49" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO49" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>08-24 19:00</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>26沂发01</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>283785.SH</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>新沂经济开发区建设发展有限公司</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>江苏省-徐州市</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>24沂发03</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>3.00Y</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>1.8412</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>申港证券股份有限公司,国泰海通证券股份有限公司,国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>江苏钟吾城乡投资发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>新沂经济开发区建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AE50" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AF50" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG50" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AH50" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AI50" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ50" s="2" t="inlineStr"/>
+      <c r="AK50" s="2" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AL50" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM50" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>08-24 19:00</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>26东财R2</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>283748.SH</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>东营市财金投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>山东省-东营市</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>25东财01</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>3.50Y</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>1.9014</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>浙商证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>东营市财金投资集团有限公司2026年面向专业投资者非公开发行一带一路公司债券(第一期)(品种二)</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AE51" s="2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AF51" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AG51" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH51" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AI51" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AJ51" s="2" t="inlineStr"/>
+      <c r="AK51" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL51" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM51" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>08-24 18:00</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>26西安经发MTN001</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>102683306.IB</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>西安经发控股(集团)有限责任公司</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>陕西省-西安市</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>24西安经发MTN001</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>248D</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>1.6234</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>国金证券股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>西安经发控股(集团)有限责任公司2026年度第一期中期票据</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AE52" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF52" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AG52" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AH52" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AI52" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AJ52" s="2" t="inlineStr"/>
+      <c r="AK52" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL52" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM52" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>08-24 19:00</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>26青城11</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>283744.SH</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>5+3+2</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>青岛城市建设投资(集团)有限责任公司</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>山东省-青岛市</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>26青城09</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>4.65Y+5.00Y</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>1.9742</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,招商证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>青岛城市建设投资(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第六期)(品种一)</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>2036-08-26</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AE53" s="2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AF53" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AG53" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AH53" s="2" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AI53" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AJ53" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="AK53" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL53" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AM53" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>08-24 19:00</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>26郑安02</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>283741.SH</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>郑州城发安居科技有限公司</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>河南省-郑州市</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>26郑安01</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>4.78Y</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2.0141</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>华泰联合证券有限责任公司,平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>郑州城发安居科技有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AE54" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AF54" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+      <c r="AG54" s="2" t="inlineStr">
+        <is>
+          <t>综合地产</t>
+        </is>
+      </c>
+      <c r="AH54" s="2" t="inlineStr">
+        <is>
+          <t>综合地产</t>
+        </is>
+      </c>
+      <c r="AI54" s="2" t="inlineStr">
+        <is>
+          <t>计算机应用</t>
+        </is>
+      </c>
+      <c r="AJ54" s="2" t="inlineStr"/>
+      <c r="AK54" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AL54" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AM54" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AN54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AO54" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>